--- a/artfynd/A 26206-2025 artfynd.xlsx
+++ b/artfynd/A 26206-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90802650</v>
+        <v>90802652</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509266.1461763655</v>
+        <v>508815</v>
       </c>
       <c r="R2" t="n">
-        <v>7047785.946756983</v>
+        <v>7047612</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,14 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +764,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogar med hög bonitet</t>
+          <t>Möjlig kalkbarrskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Grov sälg</t>
+          <t>Asp (ca 30 cm dbh)</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -806,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90802649</v>
+        <v>90802665</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509266.1461763655</v>
+        <v>509040</v>
       </c>
       <c r="R3" t="n">
-        <v>7047785.946756983</v>
+        <v>7047712</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,21 +864,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,11 +881,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Skogar med hög bonitet</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Grov sälg</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -937,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90802654</v>
+        <v>90801893</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509261.9307147728</v>
+        <v>509166</v>
       </c>
       <c r="R4" t="n">
-        <v>7047854.128620799</v>
+        <v>7047847</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,21 +975,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1041,7 +996,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Gammal rönn</t>
+          <t>Rönn</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1068,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90802658</v>
+        <v>90802650</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1108,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509294.7797210285</v>
+        <v>509266</v>
       </c>
       <c r="R5" t="n">
-        <v>7047914.840288918</v>
+        <v>7047786</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,21 +1091,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1172,7 +1112,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Grov asp</t>
+          <t>Grov sälg</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1199,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90802657</v>
+        <v>90801892</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509266.8088389139</v>
+        <v>509166</v>
       </c>
       <c r="R6" t="n">
-        <v>7047864.839825117</v>
+        <v>7047847</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1272,21 +1207,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1303,7 +1228,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Grov sälg (&gt; 60 cm dbh)</t>
+          <t>Grov asp (&gt; 40 cm dbh)</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1330,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90801892</v>
+        <v>90802646</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509165.9953980384</v>
+        <v>509239</v>
       </c>
       <c r="R7" t="n">
-        <v>7047847.164938962</v>
+        <v>7047828</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1403,21 +1323,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1434,7 +1344,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Grov asp (&gt; 40 cm dbh)</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1461,15 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90802653</v>
+        <v>90802648</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509240.9727329147</v>
+        <v>509113</v>
       </c>
       <c r="R8" t="n">
-        <v>7047847.827705231</v>
+        <v>7047732</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1534,21 +1439,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1565,7 +1460,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Rönn</t>
+          <t>Grov asp</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1592,37 +1487,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90802665</v>
+        <v>90802651</v>
       </c>
       <c r="B9" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1632,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509040.074843787</v>
+        <v>509266</v>
       </c>
       <c r="R9" t="n">
-        <v>7047712.197289973</v>
+        <v>7047786</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1665,21 +1555,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1692,6 +1572,11 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Skogar med hög bonitet</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Grov sälg</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1718,15 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>90801893</v>
+        <v>90802653</v>
       </c>
       <c r="B10" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,21 +1614,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1758,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509165.9953980384</v>
+        <v>509241</v>
       </c>
       <c r="R10" t="n">
-        <v>7047847.164938962</v>
+        <v>7047848</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1791,19 +1671,9 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-08-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1849,15 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>90802651</v>
+        <v>90802654</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509266.1461763655</v>
+        <v>509262</v>
       </c>
       <c r="R11" t="n">
-        <v>7047785.946756983</v>
+        <v>7047854</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1922,21 +1787,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1953,7 +1808,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Grov sälg</t>
+          <t>Gammal rönn</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -1980,15 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>90802652</v>
+        <v>90802657</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2020,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508814.9586486369</v>
+        <v>509267</v>
       </c>
       <c r="R12" t="n">
-        <v>7047612.16623487</v>
+        <v>7047865</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2053,26 +1903,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2084,12 +1919,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Möjlig kalkbarrskog</t>
+          <t>Skogar med hög bonitet</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Asp (ca 30 cm dbh)</t>
+          <t>Grov sälg (&gt; 60 cm dbh)</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2116,15 +1951,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>90802648</v>
+        <v>90802658</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2156,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509113.2151580076</v>
+        <v>509295</v>
       </c>
       <c r="R13" t="n">
-        <v>7047732.018084106</v>
+        <v>7047915</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2189,19 +2019,9 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-08-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,12 +2070,7 @@
         <v>90801891</v>
       </c>
       <c r="B14" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509165.9953980384</v>
+        <v>509166</v>
       </c>
       <c r="R14" t="n">
-        <v>7047847.164938962</v>
+        <v>7047847</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2320,19 +2135,9 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-08-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2378,37 +2183,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>90802646</v>
+        <v>90802649</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2418,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509238.7982173662</v>
+        <v>509266</v>
       </c>
       <c r="R15" t="n">
-        <v>7047828.210107955</v>
+        <v>7047786</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2451,21 +2251,11 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2482,7 +2272,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Grov sälg</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2512,12 +2302,7 @@
         <v>91133415</v>
       </c>
       <c r="B16" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2549,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508959.0467600666</v>
+        <v>508959</v>
       </c>
       <c r="R16" t="n">
-        <v>7047640.204875305</v>
+        <v>7047640</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2582,19 +2367,9 @@
           <t>2019-08-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-08-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
